--- a/public/templates/data_terpilah.xlsx
+++ b/public/templates/data_terpilah.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wamp64\www\dinsos-sipandakabulan-ci4\public\template_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B1CA2B3-433D-4B3F-9F9B-583244656867}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8712F417-C014-4A9C-B36F-20DDE686E248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A935C8DA-C60F-4F6E-84BF-5A691A2D3E4C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A935C8DA-C60F-4F6E-84BF-5A691A2D3E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -340,10 +340,58 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -356,80 +404,32 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -747,568 +747,667 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14467B52-DFB8-4534-B28E-D868E30419C8}">
   <dimension ref="A3:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="5" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="5">
-        <v>2021</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5">
-        <v>2022</v>
-      </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="5" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="23">
+        <v>2024</v>
+      </c>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23">
+        <v>2025</v>
+      </c>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
+      <c r="K5" s="23"/>
+      <c r="L5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
+      <c r="M5" s="23"/>
+      <c r="N5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5" t="s">
+      <c r="O5" s="23"/>
+      <c r="P5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="14">
+      <c r="Q5" s="23"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-    </row>
-    <row r="7" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="14">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-    </row>
-    <row r="8" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="14">
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>3</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-    </row>
-    <row r="9" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="14">
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>4</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-    </row>
-    <row r="10" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="14">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-    </row>
-    <row r="11" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="14">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>6</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-    </row>
-    <row r="12" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="14">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>7</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-    </row>
-    <row r="13" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="14">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>8</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-    </row>
-    <row r="14" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="14">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="14">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>10</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-    </row>
-    <row r="16" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="14">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>11</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-    </row>
-    <row r="17" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="14">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-    </row>
-    <row r="18" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="14">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>13</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-    </row>
-    <row r="19" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="14">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>14</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-    </row>
-    <row r="20" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="14">
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>15</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-    </row>
-    <row r="21" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="14">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
         <v>16</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-    </row>
-    <row r="22" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="14">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
         <v>17</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-    </row>
-    <row r="23" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="14">
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>18</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-    </row>
-    <row r="24" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="14">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>19</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-    </row>
-    <row r="25" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="14">
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>20</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-    </row>
-    <row r="26" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="14">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>21</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="114">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I5"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
     <mergeCell ref="B26:I26"/>
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="L26:M26"/>
@@ -1324,105 +1423,6 @@
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I5"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
